--- a/VerveStacks_BIH_grids_kan10/source_data/VerveStacks_BIH.xlsx
+++ b/VerveStacks_BIH_grids_kan10/source_data/VerveStacks_BIH.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7CB02A5-492F-4C11-A6C4-92179020FC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A205AF3F-BD82-4791-9341-8E9DEFB773FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1357,7 +1357,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{996AC68C-38BC-D40E-94A5-D7CDB0FE7818}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A5A56A9-C5E6-AB39-DD88-EC0717733095}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1708,7 +1708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A98942D-7E6F-4625-AA4A-2CF0D8B0DD17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41067C7-2125-44C1-80AA-EC823C0BC7D7}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4836,7 +4836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A258E25D-04D0-4CD9-9B80-732FB299E392}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F81F6085-68C5-46F4-8178-AFD6D97F14FA}">
   <dimension ref="B2:L12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5201,7 +5201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3464FF77-1275-4BCC-954F-24B366BDE25E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6CBC3ED-23CF-4ABE-BD3F-7B5452AA6104}">
   <dimension ref="B2:J13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5535,7 +5535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DD9067-F7B8-4797-BC18-12EC8A923B74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5884A34E-5E64-4B95-91CD-B31BBEEF6719}">
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5945,7 +5945,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CFDB297-2B10-4B31-BA2F-5D09EC46C394}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8CB34A-B6A3-42D9-A7C4-B55C8FE516D2}">
   <dimension ref="A1:AD119"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11059,7 +11059,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T86">
-        <v>0.18526537357485862</v>
+        <v>0.18526537357485859</v>
       </c>
       <c r="U86">
         <v>0</v>
@@ -11106,7 +11106,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T87">
-        <v>0.18526537357485862</v>
+        <v>0.18526537357485859</v>
       </c>
       <c r="U87">
         <v>0</v>
@@ -11153,7 +11153,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="T88">
-        <v>0.18526537357485862</v>
+        <v>0.18526537357485859</v>
       </c>
       <c r="U88">
         <v>0</v>
